--- a/results/momentum_merged_2026-10-06.xlsx
+++ b/results/momentum_merged_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,1748 +451,1660 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BZFD</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>BOT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIIA</t>
+          <t>ABSI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>ATOM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FUFU</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>ABXL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GNLN</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ATII</t>
+          <t>BTTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>DUKRW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CRD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CRNT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>ADPT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CRUS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>KBSX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>AEHL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FLEX</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GSRF</t>
+          <t>DUOT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MDAI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>EMPD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>AFRI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KFII</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>HBANL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>AIB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>HYPR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NSLRL</t>
+          <t>INEO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>ALAB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>IQMX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ITRN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ALNT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>MIND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>AMBR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEON</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>QUIK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RYAAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARAY</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLMT</t>
+          <t>SNWV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>ASST</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARW</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>ATKR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>TLN</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>AVAT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>AXTI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BATRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BELFB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SXTP</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUUD</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>THEO</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>CBAT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BKHA</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLRK</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>CEVA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BTTC</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>COHR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>CVCO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CWBC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>DSGR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>EGHT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CWBC</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EUDA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>FEIM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>FMAO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>FROG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FNRN</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>FWDI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>HBIO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>INKT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>IRDM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>KFII</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KMRK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INCR</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>LEDS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KCHV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KOSS</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MCHPP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MSGY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>MTSI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NOVT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MNTK</t>
+          <t>NTCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NTRP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NVEC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>OUST</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>PWP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAYO</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RMBS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PLUN</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PLXS</t>
+          <t>SBET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>QSEA</t>
+          <t>SILC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SIMO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SITM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>SMTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SPOK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SAX</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>STRK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>SVCO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SIGA</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>TITN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TLSA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>TRNI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>TRNS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>USDEW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>WLTH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUIG</t>
+          <t>COHU</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>CRVO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SVIA</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>ICHR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SWBI</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>IMMP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>REBN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>XFLH</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>XRPNU</t>
+          <t>SLGL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>PAHC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IMMP</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>IMOS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>BTLN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>XRPN</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>STKE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OCG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>MKSI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SYNA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>TJGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>ENTG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>AXTI</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>KLIC</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CD</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>QMCO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ACLS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MASS</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ASYS</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SANG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PMVP</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>REBN</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>PACB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
